--- a/HTR-update-ML/ig/StructureDefinition-fr-lm-commentaire-er.xlsx
+++ b/HTR-update-ML/ig/StructureDefinition-fr-lm-commentaire-er.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T12:45:48+00:00</t>
+    <t>2026-03-17T12:52:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
